--- a/Result/profitability/8101.xlsx
+++ b/Result/profitability/8101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7675</v>
+        <v>-0.7649999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>16.56125</v>
+        <v>21.15625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7212499999999999</v>
+        <v>-0.68625</v>
       </c>
       <c r="N3" t="n">
-        <v>20.84625</v>
+        <v>11.99625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5962499999999999</v>
+        <v>-0.445</v>
       </c>
       <c r="N4" t="n">
-        <v>11.645</v>
+        <v>11.31625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5475</v>
+        <v>-0.6025</v>
       </c>
       <c r="N5" t="n">
-        <v>10.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5137499999999999</v>
+        <v>-0.475</v>
       </c>
       <c r="N6" t="n">
-        <v>8.893750000000001</v>
+        <v>7.177500000000002</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4025</v>
+        <v>-0.36</v>
       </c>
       <c r="N7" t="n">
-        <v>7.027500000000002</v>
+        <v>6.092500000000002</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.295</v>
+        <v>-0.24125</v>
       </c>
       <c r="N8" t="n">
-        <v>5.877500000000001</v>
+        <v>6.978750000000002</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.2</v>
       </c>
       <c r="N9" t="n">
-        <v>6.275000000000002</v>
+        <v>6.275000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>-0.22625</v>
       </c>
       <c r="N10" t="n">
-        <v>6.020000000000002</v>
+        <v>6.020000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>104</v>
+      </c>
+      <c r="D75" t="n">
+        <v>94</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-27.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.78875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.10375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4299999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4526315789473684</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.279999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4861183865898376</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
